--- a/data/planning/AMS Planejamento.xlsx
+++ b/data/planning/AMS Planejamento.xlsx
@@ -125,10 +125,10 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="æ¸¸ã´ã·ãã¯ Light"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="ç­çº¿ Light"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¦Â¸Â¸Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯ Light"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã§Â­ÂÃ§ÂºÂ¿ Light"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -177,10 +177,10 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="æ¸¸ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="ç­çº¿"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¦Â¸Â¸Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã§Â­ÂÃ§ÂºÂ¿"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -706,43 +706,43 @@
         <v>Módulo 4 — Sobrevivência, inferência causal e decisão.</v>
       </c>
     </row>
-    <row r="15" ht="46.79999999999999" customHeight="1" xml:space="preserve">
+    <row r="15" ht="46.79999999999999" customHeight="1">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="1">
         <v>46332</v>
       </c>
-      <c r="C15" t="str" xml:space="preserve">
+      <c r="C15" t="str">
+        <v>Apresentação de artigo 2</v>
+      </c>
+      <c r="E15" t="str">
+        <v>apresentacao</v>
+      </c>
+      <c r="F15" t="str">
+        <v>planned</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Módulo 5 — Ética, regulação e prática profissional.</v>
+      </c>
+    </row>
+    <row r="16" ht="15.6" customHeight="1" xml:space="preserve">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46339</v>
+      </c>
+      <c r="C16" t="str" xml:space="preserve">
         <v xml:space="preserve">Aula 13: Sistemas de apoio à decisão clínica e implementação_x000d_
 Aula 14: Explicabilidade, equidade e privacidade_x000d_
 Aula 15: Regulação, relato científico e MLOps</v>
       </c>
-      <c r="D15" t="str">
+      <c r="D16" t="str">
         <v>BERNER (2007); WORLD HEALTH ORGANIZATION (2021); ANVISA (2022); FDA (2025); COLLINS et al. (2024)</v>
       </c>
-      <c r="E15" t="str">
-        <v>aula</v>
-      </c>
-      <c r="F15" t="str">
-        <v>planned</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Módulo 5 — Ética, regulação e prática profissional.</v>
-      </c>
-    </row>
-    <row r="16" ht="15.6" customHeight="1">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1">
-        <v>46339</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Apresentação de artigo 2</v>
-      </c>
       <c r="E16" t="str">
-        <v>apresentacao</v>
+        <v>aula</v>
       </c>
       <c r="F16" t="str">
         <v>planned</v>

--- a/data/planning/AMS Planejamento.xlsx
+++ b/data/planning/AMS Planejamento.xlsx
@@ -125,10 +125,10 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¦Â¸Â¸Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯ Light"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã§Â­ÂÃ§ÂºÂ¿ Light"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂ¦ÃÂ¸ÃÂ¸ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯ Light"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ§ÃÂ­ÃÂÃÂ§ÃÂºÃÂ¿ Light"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -177,10 +177,10 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¦Â¸Â¸Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã§Â­ÂÃ§ÂºÂ¿"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂ¦ÃÂ¸ÃÂ¸ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ§ÃÂ­ÃÂÃÂ§ÃÂºÃÂ¿"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -662,28 +662,27 @@
         <v>Módulo 3 — Aprendizado profundo e NLP.</v>
       </c>
     </row>
-    <row r="13" ht="34.05" customHeight="1" xml:space="preserve">
+    <row r="13" ht="34.05" customHeight="1">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="1">
         <v>46318</v>
       </c>
-      <c r="C13" t="str" xml:space="preserve">
-        <v xml:space="preserve">Aula 11: Análise de sobrevivência, predição de risco_x000d_
-Aula 12: Inferência causal e evidência de mundo real</v>
+      <c r="C13" t="str">
+        <v>Não haverá aula</v>
       </c>
       <c r="D13" t="str">
-        <v>WANG; LI; REDDY (2019); HERNÁN; ROBINS (2020)</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>aula</v>
+        <v>sem-aula</v>
       </c>
       <c r="F13" t="str">
-        <v>planned</v>
+        <v>changed</v>
       </c>
       <c r="G13" t="str">
-        <v>Módulo 4 — Sobrevivência, inferência causal e decisão.</v>
+        <v/>
       </c>
     </row>
     <row r="14" ht="15.6" customHeight="1">
